--- a/frontend/public/prep-runway/prep-runway-google-sheets-2026-05-22.xlsx
+++ b/frontend/public/prep-runway/prep-runway-google-sheets-2026-05-22.xlsx
@@ -19,12 +19,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Ledger'!$A$1:$U$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Meal Timing'!$A$1:$J$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Training'!$A$1:$O$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sleep Recovery'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Meal Timing'!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Training'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sleep Recovery'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Feedback Loop'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Runway Narrative'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Food Log Raw'!$A$1:$N$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Food Log Raw'!$A$1:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'MacroFactor Daily'!$A$1:$Q$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -205,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MealTiming" displayName="MealTiming" ref="A1:J22" headerRowCount="1">
-  <autoFilter ref="A1:J22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MealTiming" displayName="MealTiming" ref="A1:J23" headerRowCount="1">
+  <autoFilter ref="A1:J23"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day"/>
@@ -224,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Training" displayName="Training" ref="A1:O19" headerRowCount="1">
-  <autoFilter ref="A1:O19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Training" displayName="Training" ref="A1:O23" headerRowCount="1">
+  <autoFilter ref="A1:O23"/>
   <tableColumns count="15">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="session_order"/>
@@ -248,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SleepRecovery" displayName="SleepRecovery" ref="A1:O6" headerRowCount="1">
-  <autoFilter ref="A1:O6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SleepRecovery" displayName="SleepRecovery" ref="A1:O7" headerRowCount="1">
+  <autoFilter ref="A1:O7"/>
   <tableColumns count="15">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day"/>
@@ -313,8 +313,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FoodLogRaw" displayName="FoodLogRaw" ref="A1:N29" headerRowCount="1">
-  <autoFilter ref="A1:N29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FoodLogRaw" displayName="FoodLogRaw" ref="A1:N35" headerRowCount="1">
+  <autoFilter ref="A1:N35"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Time"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22 11:01 AM</t>
+          <t>2026-05-22 09:18 PM</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>963 cal / 174P / 11.8F / 35.5C</t>
+          <t>917 cal / 162P / 12.7F / 34.9C</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Current check-in</t>
+          <t>Aggressive/Recoverable D2</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
@@ -1342,28 +1342,66 @@
       <c r="E7" s="5" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>7h25m</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>7h25m</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>688</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Stair 50:37 + Stair 50:00</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Pull 108:07</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>11987</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>1901</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>116.6</v>
+      </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>flat-ish but still down 10.6 lb from 5/17 — Use marker-led cardio and GI-friendly protein.</t>
+          <t>Workout/day totals locked; macros still partial at 688 cal / 101P. PM Stair added and day became high-output.</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>cleanup-feedback-loop-may17-jun1-2026.csv; user-reported 158.4 lb</t>
+          <t>MacroFactor export 2026-05-22 17:42 + Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2342,31 +2380,83 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>11:33a</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>No food logged in export yet</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
+          <t>Chicken + egg whites + avocado + turkey bacon</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>451</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Use feedback loop today.</t>
+          <t>Whole-food base; better GI structure than all-powder days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>3:17p</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Banana + chocolate nutrition shake</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Pre-lift fuel; controlled carb bump before pull day.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J22"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2380,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2485,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="48" customWidth="1" min="14" max="14"/>
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
@@ -3605,8 +3695,258 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>7:03 AM</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>7:54 AM</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>50:37</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Z3 moderate</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>AM stair was controlled lower-HR output than Wed/Thu; useful anchor without spiking too hard.</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Claude Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>3:43 PM</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>3:44 PM</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Warmup</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>1:16</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Z1/Z2</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Raw context only; excluded from readable ledger per user preference.</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Claude Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>3:45 PM</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>5:33 PM</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Pull day</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>108:07</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>606</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Z2/Z3</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>Long pull day; lower HR than Thu but user felt deficit around minute 60, so do not interpret the lower burn as room to add punishment volume.</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>MacroFactor workout log + Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>5:35 PM</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>6:25 PM</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>50:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Z3 moderate with spike</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>PM StairMaster matched AM average effort but peaked at 175 after the long pull day; useful output, but this is a hard post-lift spike and should count as high stress.</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3620,7 +3960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4074,8 +4414,81 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>11:58p Thu</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>7:29a</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>7h25m</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>4h38m</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>2h10m</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>35m</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Good recovery marker day before another high-output training day.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4096,7 +4509,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -4417,32 +4830,32 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>GI check pending</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>stool check pending</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>deficit felt during lift after ~60m</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>needs check-in</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>needs check-in</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>needs check-in</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>needs check-in</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>needs check-in</t>
-        </is>
-      </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>needs check-in</t>
+          <t>pull day plus two StairMasters; PM stair peaked 175</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -4452,7 +4865,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Use marker-led cardio and GI-friendly protein.</t>
+          <t>Do not add more training today. Finish final macros and use Sat AM weight/RHR/HRV/sleep to decide whether to keep aggressive or pull back.</t>
         </is>
       </c>
     </row>
@@ -4856,7 +5269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6375,8 +6788,308 @@
       </c>
       <c r="N29" s="5" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>11:33 AM</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Chicken Breasts</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>oz</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>473.2</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>11:33 AM</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Egg Whites</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>11:33 AM</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Organic Avocado Mash</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>11:33 AM</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Uncured Turkey Bacon Turkey Thighs Chopped and Formed</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>serving</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>03:17 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Banana, Fresh</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>03:17 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate Nutrition Shake</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N29"/>
+  <autoFilter ref="A1:N35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6806,21 +7519,45 @@
         <v>151.42</v>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>688</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="M8" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
+        <v>8032</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>1256.3</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>2061.1</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>42.2</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q8"/>

--- a/frontend/public/prep-runway/prep-runway-google-sheets-2026-05-22.xlsx
+++ b/frontend/public/prep-runway/prep-runway-google-sheets-2026-05-22.xlsx
@@ -18,13 +18,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MacroFactor Daily" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Ledger'!$A$1:$U$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Meal Timing'!$A$1:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Training'!$A$1:$O$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sleep Recovery'!$A$1:$O$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Feedback Loop'!$A$1:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Runway Narrative'!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Food Log Raw'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Ledger'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Meal Timing'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Training'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sleep Recovery'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Feedback Loop'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Runway Narrative'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Food Log Raw'!$A$1:$N$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'MacroFactor Daily'!$A$1:$Q$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -175,8 +175,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyLedger" displayName="DailyLedger" ref="A1:U7" headerRowCount="1">
-  <autoFilter ref="A1:U7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DailyLedger" displayName="DailyLedger" ref="A1:U10" headerRowCount="1">
+  <autoFilter ref="A1:U10"/>
   <tableColumns count="21">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day"/>
@@ -205,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MealTiming" displayName="MealTiming" ref="A1:J23" headerRowCount="1">
-  <autoFilter ref="A1:J23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MealTiming" displayName="MealTiming" ref="A1:J29" headerRowCount="1">
+  <autoFilter ref="A1:J29"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day"/>
@@ -224,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Training" displayName="Training" ref="A1:O23" headerRowCount="1">
-  <autoFilter ref="A1:O23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Training" displayName="Training" ref="A1:O27" headerRowCount="1">
+  <autoFilter ref="A1:O27"/>
   <tableColumns count="15">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="session_order"/>
@@ -248,8 +248,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SleepRecovery" displayName="SleepRecovery" ref="A1:O7" headerRowCount="1">
-  <autoFilter ref="A1:O7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SleepRecovery" displayName="SleepRecovery" ref="A1:O9" headerRowCount="1">
+  <autoFilter ref="A1:O9"/>
   <tableColumns count="15">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day"/>
@@ -272,27 +272,28 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeedbackLoop" displayName="FeedbackLoop" ref="A1:J7" headerRowCount="1">
-  <autoFilter ref="A1:J7"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FeedbackLoop" displayName="FeedbackLoop" ref="A1:K10" headerRowCount="1">
+  <autoFilter ref="A1:K10"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="am_weight_lb"/>
     <tableColumn id="3" name="gi_stomach"/>
     <tableColumn id="4" name="stool"/>
     <tableColumn id="5" name="energy"/>
     <tableColumn id="6" name="hunger"/>
-    <tableColumn id="7" name="soreness"/>
-    <tableColumn id="8" name="training_readiness"/>
-    <tableColumn id="9" name="scale_read"/>
-    <tableColumn id="10" name="adjustment"/>
+    <tableColumn id="7" name="drive"/>
+    <tableColumn id="8" name="soreness"/>
+    <tableColumn id="9" name="training_readiness"/>
+    <tableColumn id="10" name="scale_read"/>
+    <tableColumn id="11" name="adjustment"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RunwayNarrative" displayName="RunwayNarrative" ref="A1:M6" headerRowCount="1">
-  <autoFilter ref="A1:M6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RunwayNarrative" displayName="RunwayNarrative" ref="A1:M9" headerRowCount="1">
+  <autoFilter ref="A1:M9"/>
   <tableColumns count="13">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="day_label"/>
@@ -313,8 +314,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FoodLogRaw" displayName="FoodLogRaw" ref="A1:N35" headerRowCount="1">
-  <autoFilter ref="A1:N35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FoodLogRaw" displayName="FoodLogRaw" ref="A1:N50" headerRowCount="1">
+  <autoFilter ref="A1:N50"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Time"/>
@@ -673,7 +674,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22 09:18 PM</t>
+          <t>2026-05-25 04:29 PM</t>
         </is>
       </c>
     </row>
@@ -697,7 +698,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>158.4 lb</t>
+          <t>154.6 lb</t>
         </is>
       </c>
     </row>
@@ -709,7 +710,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>-10.6 lb</t>
+          <t>-14.4 lb</t>
         </is>
       </c>
     </row>
@@ -721,7 +722,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>917 cal / 162P / 12.7F / 34.9C</t>
+          <t>1007 cal / 174P / 15.3F / 38.8C</t>
         </is>
       </c>
     </row>
@@ -772,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -788,7 +789,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
@@ -1358,16 +1359,16 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>688</v>
+        <v>1113</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>101</v>
+        <v>186</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
@@ -1396,17 +1397,254 @@
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>Workout/day totals locked; macros still partial at 688 cal / 101P. PM Stair added and day became high-output.</t>
+          <t>Final macros closed at 1113 cal / 186P / 21F / 40C. Workout/day totals locked; PM Stair added and day became high-output.</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>MacroFactor export 2026-05-22 17:42 + Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
+          <t>User final macro correction pasted in Codex chat 2026-05-22 + Claude full-session Apple Health pull pasted in Codex chat 2026-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Aggressive/Recoverable D3</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>7h47m</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>7h47m</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>956</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Stair 62:00</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Arms/shoulders 120:00</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>8029</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>1245</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>Sat closed controlled but still aggressive: 956 cal / 170.9P / 10.3F / 43.6C, one 2h lift, one 62m StairMaster, 8,029 steps, adjusted active ~1,070. Lighter than Friday and recovery markers stayed usable.</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>MacroFactor-20260524131530.xlsx + Claude Sat 5/23 workout/day totals pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Aggressive/Recoverable D4</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>6h40m</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>6h40m</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1170</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Stair 80:48</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>No lift</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>13095</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>1251</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>Sunday closed as cardio-only but still hard: 1,170 cal / 166P / 32F / 49C, one 80:48 StairMaster at avg HR 143 / max 157, 13,095 steps, Apple active 1,251. RHR hit true baseline at 42; not a refeed day.</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>User AM weigh-in + Claude Sun 5/24 Apple Health nutrition/sleep/cardio/day totals pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Current check-in</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Leg day planned</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>AM weight 154.6: down 1.7 from Sunday and almost exactly at the 154.5 Monday forecast center. This is on target, not a stall; need Monday sleep/recovery, macros, cardio/lift, and subjective check-in to close the day.</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>User AM weigh-in pasted in Codex chat 2026-05-25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1420,13 +1658,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -2455,8 +2693,272 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>timing pending</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Final macro closeout / user-reported remainder</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Reconciles the partial 688 cal export to the user-reported final 1113 cal / 186P / 21F / 40C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>12:15p</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate nutrition shake</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Powder anchor before training; simple but still shake-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>12:47p</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Measured carb before the lift; useful training support with nearly no fat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>5:00-5:22p</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate shakes + egg whites</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>425</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Post-training protein cluster after lift and StairMaster; high protein but still powder-heavy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>7:40p</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate nutrition shake</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Additional powder meal; keeps protein covered but does not improve food-form stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>9:30p</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Egg whites</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Low-fat whole-food protein closeout.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2470,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3945,8 +4447,260 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>1:07 PM</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>1:12 PM</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Warmup</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Raw context only; excluded from readable ledger per user preference.</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sat 5/23 workout pull pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>1:12 PM</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>3:13 PM</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Arms/Shoulders</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2:00:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Z1/Z2</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Light controlled lift after a high-output Friday; avg HR 83 confirms this was not another dense overreach lift. Strength calories discounted about 50% for planning.</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sat 5/23 workout pull pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>3:13 PM</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>4:14 PM</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>1:02:00</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Z2/Z3</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Single post-lift StairMaster block; lower peak than Friday PM stair and useful controlled output without the 175 bpm spike.</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sat 5/23 workout pull pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>7:11 PM</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>8:32 PM</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>1:20:48</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>928</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>928</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Z3/Z4</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Cardio-only day but this was a hard 80-minute StairMaster block. Avg HR 143 and 928 kcal make it a real stressor before Monday leg day; count it as high-output cardio, not easy recovery.</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sun 5/24 cardio/day totals pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3960,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4487,8 +5241,154 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>12:10a</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>8:27a</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>7h47m</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>8h17m</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>4h47m</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>2h05m</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>55m</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Strong sleep and RHR; HRV dipped from 116.6 after Friday volume but remains usable.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Claude sleep/recovery pull pasted in Codex chat 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>11:58p Sat</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>7:02a</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>6h40m</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>7h04m</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>4h10m</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>1h43m</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>47m</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>RHR hit true baseline; sleep was shorter than Saturday but efficient enough for a cardio-only close.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Claude Sun 5/24 sleep/recovery pull pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O7"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4502,7 +5402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4511,10 +5411,11 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4550,20 +5451,25 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>drive</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>soreness</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>training_readiness</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>scale_read</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>adjustment</t>
         </is>
@@ -4600,20 +5506,25 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
           <t>leg soreness after leg day</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>start point</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>No change.</t>
         </is>
@@ -4655,15 +5566,20 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
           <t>high output</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>strong flush</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Keep aggressive but do not add extra punishment cardio.</t>
         </is>
@@ -4705,15 +5621,20 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
           <t>overreach</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>flush continued</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Pull back if sleep/recovery weak.</t>
         </is>
@@ -4755,15 +5676,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
           <t>no lift; high walking</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>flush continued</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>No lift helped; protect sleep.</t>
         </is>
@@ -4805,15 +5731,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
           <t>dense lift plus two StairMasters</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>small next-day drop likely masked by training/GI water</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Shift more protein to whole foods; reduce powder boluses.</t>
         </is>
@@ -4855,22 +5786,192 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
+          <t>needs check-in</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
           <t>pull day plus two StairMasters; PM stair peaked 175</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>flat-ish but still down 10.6 lb from 5/17</t>
-        </is>
-      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Do not add more training today. Finish final macros and use Sat AM weight/RHR/HRV/sleep to decide whether to keep aggressive or pull back.</t>
+          <t>flat-ish but still down 10.6 lb from 5/17; final macros 1113 cal / 186P / 21F / 40C</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Do not add more training today. Use Sat AM weight/RHR/HRV/sleep plus GI/hunger to decide whether to keep aggressive or pull back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>GI check pending</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Stool check pending</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Controlled lift plus one StairMaster: 2h lift avg HR 83, 62m Stair avg HR 128, 8,029 steps, adjusted active ~1,070</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Strong drop: 158.4 to 157.0 after Friday high output; Saturday did not look like a stall or rebound. Protein hit, calories stayed very low, and output was lighter than Friday.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Stay aggressive but controlled. Next lever is measured food quality/pre-lift carbs if performance dips, not extra cardio volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>GI check pending</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Stool check pending</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Good; score pending</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Needs score</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Good; score pending</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Cardio-only but hard: 80:48 StairMaster, avg HR 143, max 157, 928 kcal, 13,095 steps</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Down 0.7 from Sat and 12.7 from 5/17; this is not a stall. RHR hit baseline at 42 and calories stayed low at 1,170.</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>No refeed yet. If energy and drive stay good and physical markers stay good, continue pushing; track Energy/Hunger/Drive as 1-10 instead of guessing cortisol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>GI check pending</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Stool check pending</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Needs score</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Needs score</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Needs score</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Needs check-in</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Leg day planned</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Down 1.7 from Sun and 14.4 from 5/17; landed essentially on the 154.5 forecast center.</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>No stall. Keep aggressive if Energy/Hunger/Drive and leg-day performance stay usable; need full Monday close before changing levers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4884,7 +5985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5254,8 +6355,171 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Aggressive/recoverable D3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>7h47m asleep; 8h17m in bed; bed 12:10a; wake 8:27a; Core 4h47m / REM 2h05m / Deep 55m / Awake 24m; RHR 44; HRV 105.7</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>956</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster 3:13-4:14 PM, 1:02:00, 618 kcal, avg HR 128, peak HR 141</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Arms/shoulders 1:12-3:13 PM, 2:00:00, 450 reported/225 adjusted kcal, avg HR 83, peak HR 123</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Scale dropped 1.4 lb from Friday to 157.0 and Saturday stayed controlled: lower active burn than Friday, one post-lift StairMaster, and no high-HR spike. Protein hit while calories and fat stayed extremely low.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Keep aggressive but controlled; the useful adjustment is better food form and measured carb timing, not panic extra cardio.</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>MacroFactor-20260524131530.xlsx + Claude Sat 5/23 workout/day totals pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Aggressive/recoverable D4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>6h40m asleep; 7h04m in bed; 94% efficiency; bed 11:58p Sat; wake 7:02a; Core 4h10m / REM 1h43m / Deep 47m / Awake 24m; RHR 42; HRV 104</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>StairMaster 7:11-8:32 PM, 1:20:48, 928 kcal, avg HR 143, peak HR 157</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>No lift</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Scale reached 156.3 and RHR hit true baseline at 42. Sunday was not a refeed: 1,170 calories, 49g carbs, and an 80-minute StairMaster at avg HR 143 kept the day aggressive.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Monday is leg day: keep cardio controlled, use measured carbs if performance needs it, and do not add extra punishment volume before seeing Monday AM weight and leg output.</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>User AM weigh-in + Claude Sun 5/24 Apple Health nutrition/sleep/cardio/day totals pasted in Codex chat 2026-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Current check-in</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Leg day planned</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>AM weight 154.6 landed essentially on the 154.5 forecast center and is down 14.4 lb from 5/17. This confirms the aggressive cleanup is still moving.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Close Monday with sleep/recovery, macros, leg-day output, cardio, and Energy/Hunger/Drive before deciding whether to keep pushing or add a measured carb lever.</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>User AM weigh-in pasted in Codex chat 2026-05-25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5269,7 +6533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5363,67 +6627,67 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>01:46 PM</t>
+          <t>06:12 AM</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Clear Protein Tropical Punch</t>
+          <t>Flash Iv - Strawberry Kiwi</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>packet</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
-        <v>45</v>
+        <v>500</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>05:03 PM</t>
+          <t>10:52 AM</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Peanut Butter Cookies &amp; Cream Protein Powder</t>
+          <t>Choclate Choclate Chip Protein Powder</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -5438,22 +6702,22 @@
         <v>37</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>48</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>6</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>360</v>
@@ -5465,64 +6729,64 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>12:59 PM</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Iso Phorm White Chocolate Peanut Butter</t>
+          <t>Lemon Raspberry Wedding Cake</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>scoop</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>66</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3.03</v>
+        <v>37</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>540</v>
+        <v>67.5</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>340</v>
+        <v>172.5</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>260</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>07:39 PM</t>
+          <t>03:14 PM</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5536,100 +6800,102 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>37</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>67.5</v>
+        <v>45</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>172.5</v>
+        <v>115</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>07:00 AM</t>
+          <t>06:58 PM</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Flash Iv - Strawberry Kiwi</t>
+          <t>Lemon Raspberry Wedding Cake</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>packet</t>
+          <t>scoop</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="L6" s="5" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>80</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>11:09 AM</t>
+          <t>09:27 PM</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Choclate Choclate Chip Protein Powder</t>
+          <t>Peanut Butter Cookies &amp; Cream Protein Powder</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -5638,50 +6904,50 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>37</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>210</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>11:43 AM</t>
+          <t>10:33 AM</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Strawberry Banana Royale Lean Whey Gourmet</t>
+          <t>Choclate Choclate Chip Protein Powder</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5690,50 +6956,50 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>37</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="L8" s="5" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>115</v>
+        <v>360</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>104</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>01:34 PM</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Strawberry Banana Royale Lean Whey Gourmet</t>
+          <t>Lemon Raspberry Wedding Cake</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -5742,102 +7008,102 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>37</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="L9" s="5" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>104</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>07:41 PM</t>
+          <t>05:15 PM</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Lean whey White Chocolate Peanut Butter</t>
+          <t>Strawberry Banana Royale Lean Whey Gourmet</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>portion</t>
+          <t>scoop</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>679.7</v>
+        <v>90</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>239.8</v>
+        <v>230</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>210.2</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>07:41 PM</t>
+          <t>07:28 PM</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Loaded Protein Raspberry Tart</t>
+          <t>Farm Fed Brown Sugar, Cinnamon, Toaster Pastry</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -5846,16 +7112,16 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>33.8</v>
+        <v>31</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>2</v>
@@ -5863,890 +7129,870 @@
       <c r="J11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>06:12 AM</t>
+          <t>11:34 AM</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Flash Iv - Strawberry Kiwi</t>
+          <t>Chicken Breasts</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>packet</t>
+          <t>oz</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>7</v>
+        <v>28.35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="H12" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="n">
-        <v>500</v>
+        <v>32.5</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>700</v>
+        <v>492.1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>80</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10:52 AM</t>
+          <t>11:34 AM</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Choclate Choclate Chip Protein Powder</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>12:59 PM</t>
+          <t>11:34 AM</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Lemon Raspberry Wedding Cake</t>
+          <t>Organic Avocado Mash</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>container</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>203</v>
+        <v>90</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>67.5</v>
+        <v>220</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>172.5</v>
+        <v>270.2</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>03:14 PM</t>
+          <t>01:50 PM</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Strawberry Banana Royale Lean Whey Gourmet</t>
+          <t>Banana, Fresh</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>37</v>
-      </c>
       <c r="G15" s="5" t="n">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>45</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="n">
-        <v>115</v>
+        <v>306.4</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>104</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>06:58 PM</t>
+          <t>01:50 PM</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Lemon Raspberry Wedding Cake</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="n">
-        <v>90</v>
+        <v>375</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>230</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>208</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>09:27 PM</t>
+          <t>06:02 PM</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Peanut Butter Cookies &amp; Cream Protein Powder</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>105</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>10:33 AM</t>
+          <t>06:32 PM</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Choclate Choclate Chip Protein Powder</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>01:34 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Lemon Raspberry Wedding Cake</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>230</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>208</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>05:15 PM</t>
+          <t>11:33 AM</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Strawberry Banana Royale Lean Whey Gourmet</t>
+          <t>Chicken Breasts</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>oz</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="n">
-        <v>90</v>
+        <v>31.3</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>230</v>
+        <v>473.2</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>208</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>07:28 PM</t>
+          <t>11:33 AM</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Farm Fed Brown Sugar, Cinnamon, Toaster Pastry</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>scoop</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.5</v>
+        <v>230</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="n">
-        <v>255</v>
+        <v>375</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>195</v>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>11:34 AM</t>
+          <t>11:33 AM</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Chicken Breasts</t>
+          <t>Organic Avocado Mash</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>container</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>28.35</v>
+        <v>57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="L22" s="5" t="n">
-        <v>32.5</v>
+        <v>220</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>492.1</v>
+        <v>270.2</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>11:34 AM</t>
+          <t>11:33 AM</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Egg Whites</t>
+          <t>Uncured Turkey Bacon Turkey Thighs Chopped and Formed</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>serving</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="N23" s="5" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>11:34 AM</t>
+          <t>03:17 PM</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Organic Avocado Mash</t>
+          <t>Banana, Fresh</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>container</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>57</v>
-      </c>
       <c r="G24" s="5" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>220</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="n">
-        <v>270.2</v>
+        <v>322.7</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>01:50 PM</t>
+          <t>03:17 PM</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Banana, Fresh</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="F25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="n">
+        <v>230</v>
+      </c>
       <c r="M25" s="5" t="n">
-        <v>306.4</v>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>4.7</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>01:50 PM</t>
+          <t>07:23 PM</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Egg Whites</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="n">
-        <v>375</v>
-      </c>
       <c r="M26" s="5" t="n">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>06:02 PM</t>
+          <t>07:23 PM</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Chocolate Nutrition Shake</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>bottle</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>100</v>
-      </c>
       <c r="G27" s="5" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="5" t="n">
-        <v>230</v>
+        <v>375</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>460</v>
+        <v>375</v>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>06:32 PM</t>
+          <t>09:00 PM</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Egg Whites</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="n">
-        <v>375</v>
-      </c>
       <c r="M28" s="5" t="n">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>12:15 PM</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6791,305 +8037,1053 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>11:33 AM</t>
+          <t>12:47 PM</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Chicken Breasts</t>
+          <t>Banana, Fresh</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>28.35</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="K30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="n">
-        <v>31.3</v>
-      </c>
+      <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="n">
-        <v>473.2</v>
+        <v>391.2</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>11:33 AM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Egg Whites</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="n">
-        <v>375</v>
-      </c>
       <c r="M31" s="5" t="n">
-        <v>375</v>
+        <v>460</v>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>11:33 AM</t>
+          <t>05:16 PM</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Organic Avocado Mash</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>container</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="5" t="n">
-        <v>57</v>
-      </c>
       <c r="G32" s="5" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="n">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>270.2</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>11:33 AM</t>
+          <t>05:22 PM</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Uncured Turkey Bacon Turkey Thighs Chopped and Formed</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>serving</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L33" s="5" t="n">
-        <v>400</v>
+        <v>230</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>20</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>03:17 PM</t>
+          <t>07:40 PM</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Banana, Fresh</t>
+          <t>Chocolate Nutrition Shake</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>bottle</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="n">
+        <v>230</v>
+      </c>
       <c r="M34" s="5" t="n">
-        <v>322.7</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>4.9</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>03:17 PM</t>
+          <t>09:30 PM</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Chocolate Nutrition Shake</t>
+          <t>Egg Whites</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>12:49 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Egg Whites</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>12:49 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Egg Whites</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>12:56 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Organic Avocado Mash</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>container</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Lean Whey Fat Metabolizing Whey Protein Peanut Butter &amp; Jelly</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>scoop</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Protein Bar Salty Peanut</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>04:47 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Hazelnut &amp; Nougat Vegan Protein Bar</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>05:47 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Lean Whey Iso-Hydro Protein Powder</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>scoop</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>05:56 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hazelnut &amp; Nougat Vegan Protein Bar</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>09:00 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate Nutrition Shake By Fairlife</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
           <t>bottle</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="F44" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="G44" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="K44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="M44" s="5" t="n">
         <v>460</v>
       </c>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Banana, Fresh</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="5" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Classic Sourdough Sliced Loaf</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>245.6</v>
+      </c>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Wild Blueberries</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>12:01 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Peanut Butter</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>portion</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>12:10 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Chocolate Nutrition Shake By Fairlife</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>12:19 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Egg Whites</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7215,56 +9209,80 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>151.14</v>
+        <v>151.3</v>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="E2" s="5" t="n">
+        <v>1028</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>150</v>
+      </c>
       <c r="M2" s="5" t="n">
-        <v>7797</v>
-      </c>
-      <c r="N2" s="5" t="inlineStr"/>
-      <c r="O2" s="5" t="inlineStr"/>
-      <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr"/>
+        <v>14690</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>997.5</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>1757.5</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>863</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>151.2</v>
+        <v>151.35</v>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="n">
-        <v>873</v>
+        <v>975</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>1800</v>
@@ -7279,45 +9297,45 @@
         <v>150</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>5817</v>
+        <v>17463</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>742.5</v>
+        <v>685</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>932.5</v>
+        <v>1015</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>641</v>
+        <v>806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>151.25</v>
+        <v>151.39</v>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="n">
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>1800</v>
@@ -7332,45 +9350,45 @@
         <v>150</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10227</v>
+        <v>11994</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>1759.7</v>
+        <v>1837.5</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>1679.8</v>
+        <v>3113.7</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>828.2</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>151.3</v>
+        <v>151.42</v>
       </c>
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="n">
-        <v>1028</v>
+        <v>1113</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>1800</v>
@@ -7385,45 +9403,45 @@
         <v>150</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>14690</v>
+        <v>12285</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>22.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>997.5</v>
+        <v>2091.3</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>1757.5</v>
+        <v>3356.1</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>863</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>151.35</v>
+        <v>151.45</v>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="n">
-        <v>975</v>
+        <v>956</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>1800</v>
@@ -7438,45 +9456,45 @@
         <v>150</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>17463</v>
+        <v>8031</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>685</v>
+        <v>1670</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>1015</v>
+        <v>2981.2</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>806</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>151.39</v>
+        <v>151.48</v>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>1800</v>
@@ -7491,73 +9509,49 @@
         <v>150</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>11994</v>
+        <v>13095</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>1837.5</v>
+        <v>970</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>3113.7</v>
+        <v>1020.2</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>22.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>1934</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>151.42</v>
+        <v>151.51</v>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n">
-        <v>688</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>165</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>150</v>
-      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="n">
-        <v>8032</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>1256.3</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>2061.1</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>42.2</v>
-      </c>
+        <v>2771</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q8"/>
